--- a/results/UniteD-SRL - run span.xlsx
+++ b/results/UniteD-SRL - run span.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e3f7d4e32ee84dc4/UniVe/UniteD-SRL/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\vito\SRL\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="132" documentId="11_1EEB9EAE655331664673AAE434FE8CC552D62E15" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44E1FD46-0635-49FB-8E65-18A2FF85D402}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5C701CD-63B3-490A-82B0-72128B197DB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41895" yWindow="1365" windowWidth="22965" windowHeight="15045" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-75" yWindow="10440" windowWidth="38580" windowHeight="10545" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dependency-based" sheetId="1" r:id="rId1"/>
@@ -1103,53 +1103,53 @@
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="6">
-        <v>84.34</v>
+        <v>85.5</v>
       </c>
       <c r="J10" s="6">
-        <v>73.75</v>
+        <v>76.510000000000005</v>
       </c>
       <c r="K10" s="7">
-        <v>78.69</v>
+        <v>80.760000000000005</v>
       </c>
       <c r="L10" s="6"/>
       <c r="M10" s="6">
-        <v>37.47</v>
+        <v>37.54</v>
       </c>
       <c r="N10" s="6">
-        <v>2</v>
+        <v>3.58</v>
       </c>
       <c r="O10" s="7">
-        <v>3.8</v>
+        <v>6.53</v>
       </c>
       <c r="Q10" s="6">
-        <v>66.73</v>
+        <v>59.82</v>
       </c>
       <c r="R10" s="6">
-        <v>47.64</v>
+        <v>43.85</v>
       </c>
       <c r="S10" s="7">
-        <v>55.59</v>
+        <v>50.6</v>
       </c>
       <c r="U10" s="6">
-        <v>58.49</v>
+        <v>53.22</v>
       </c>
       <c r="V10" s="6">
-        <v>18.57</v>
+        <v>17.920000000000002</v>
       </c>
       <c r="W10" s="7">
-        <v>28.19</v>
+        <v>26.81</v>
       </c>
       <c r="Y10" s="6">
         <f>AVERAGE(I10,M10,Q10,U10)</f>
-        <v>61.757500000000007</v>
+        <v>59.019999999999996</v>
       </c>
       <c r="Z10" s="6">
         <f>AVERAGE(J10,N10,R10,V10)</f>
-        <v>35.49</v>
+        <v>35.465000000000003</v>
       </c>
       <c r="AA10" s="7">
         <f>AVERAGE(K10,O10,S10,W10)</f>
-        <v>41.567499999999995</v>
+        <v>41.175000000000004</v>
       </c>
       <c r="AB10" s="6"/>
       <c r="AC10" s="6"/>
@@ -1190,52 +1190,52 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>48.65</v>
+        <v>51.29</v>
       </c>
       <c r="J11">
-        <v>15.56</v>
+        <v>17.059999999999999</v>
       </c>
       <c r="K11" s="11">
-        <v>23.58</v>
+        <v>25.61</v>
       </c>
       <c r="M11">
-        <v>82.27</v>
+        <v>82.84</v>
       </c>
       <c r="N11">
-        <v>55.89</v>
+        <v>59.65</v>
       </c>
       <c r="O11" s="11">
-        <v>66.56</v>
+        <v>69.36</v>
       </c>
       <c r="Q11">
-        <v>44.17</v>
+        <v>50.13</v>
       </c>
       <c r="R11">
-        <v>14.42</v>
+        <v>16.559999999999999</v>
       </c>
       <c r="S11">
-        <v>21.74</v>
+        <v>24.9</v>
       </c>
       <c r="U11">
-        <v>29.99</v>
+        <v>41.31</v>
       </c>
       <c r="V11">
-        <v>6.3</v>
+        <v>9.69</v>
       </c>
       <c r="W11" s="11">
-        <v>10.41</v>
+        <v>15.7</v>
       </c>
       <c r="Y11" s="6">
         <f t="shared" ref="Y11:Y17" si="3">AVERAGE(I11,M11,Q11,U11)</f>
-        <v>51.269999999999996</v>
+        <v>56.392499999999998</v>
       </c>
       <c r="Z11" s="6">
         <f t="shared" ref="Z11:Z17" si="4">AVERAGE(J11,N11,R11,V11)</f>
-        <v>23.0425</v>
+        <v>25.74</v>
       </c>
       <c r="AA11" s="7">
         <f t="shared" ref="AA11:AA17" si="5">AVERAGE(K11,O11,S11,W11)</f>
-        <v>30.572499999999998</v>
+        <v>33.892499999999998</v>
       </c>
     </row>
     <row r="12" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1258,21 +1258,53 @@
       <c r="G12" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="K12" s="11"/>
-      <c r="O12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="W12" s="11"/>
-      <c r="Y12" s="6" t="e">
+      <c r="I12">
+        <v>86.34</v>
+      </c>
+      <c r="J12">
+        <v>77.760000000000005</v>
+      </c>
+      <c r="K12" s="11">
+        <v>81.819999999999993</v>
+      </c>
+      <c r="M12">
+        <v>82.81</v>
+      </c>
+      <c r="N12">
+        <v>60.1</v>
+      </c>
+      <c r="O12" s="11">
+        <v>69.650000000000006</v>
+      </c>
+      <c r="Q12">
+        <v>69.11</v>
+      </c>
+      <c r="R12">
+        <v>55.95</v>
+      </c>
+      <c r="S12" s="11">
+        <v>61.84</v>
+      </c>
+      <c r="U12">
+        <v>61.21</v>
+      </c>
+      <c r="V12">
+        <v>23.24</v>
+      </c>
+      <c r="W12" s="11">
+        <v>33.69</v>
+      </c>
+      <c r="Y12" s="6">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z12" s="6" t="e">
+        <v>74.867499999999993</v>
+      </c>
+      <c r="Z12" s="6">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA12" s="7" t="e">
+        <v>54.262500000000003</v>
+      </c>
+      <c r="AA12" s="7">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>61.75</v>
       </c>
     </row>
     <row r="13" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1295,21 +1327,53 @@
       <c r="G13" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="K13" s="11"/>
-      <c r="O13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="W13" s="11"/>
-      <c r="Y13" s="6" t="e">
+      <c r="I13" s="6">
+        <v>86.48</v>
+      </c>
+      <c r="J13" s="6">
+        <v>77.95</v>
+      </c>
+      <c r="K13" s="11">
+        <v>81.99</v>
+      </c>
+      <c r="M13" s="6">
+        <v>82.65</v>
+      </c>
+      <c r="N13" s="6">
+        <v>60.12</v>
+      </c>
+      <c r="O13" s="11">
+        <v>69.599999999999994</v>
+      </c>
+      <c r="Q13" s="6">
+        <v>77.16</v>
+      </c>
+      <c r="R13" s="6">
+        <v>71.78</v>
+      </c>
+      <c r="S13" s="11">
+        <v>74.37</v>
+      </c>
+      <c r="U13" s="6">
+        <v>60.89</v>
+      </c>
+      <c r="V13" s="6">
+        <v>23.1</v>
+      </c>
+      <c r="W13" s="11">
+        <v>33.5</v>
+      </c>
+      <c r="Y13" s="6">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z13" s="6" t="e">
+        <v>76.795000000000002</v>
+      </c>
+      <c r="Z13" s="6">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA13" s="7" t="e">
+        <v>58.237499999999997</v>
+      </c>
+      <c r="AA13" s="7">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>64.864999999999995</v>
       </c>
     </row>
     <row r="14" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1332,21 +1396,53 @@
       <c r="G14" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="K14" s="11"/>
-      <c r="O14" s="11"/>
-      <c r="S14" s="11"/>
-      <c r="W14" s="11"/>
-      <c r="Y14" s="6" t="e">
+      <c r="I14" s="6">
+        <v>86.16</v>
+      </c>
+      <c r="J14" s="6">
+        <v>76.94</v>
+      </c>
+      <c r="K14" s="11">
+        <v>81.290000000000006</v>
+      </c>
+      <c r="M14" s="6">
+        <v>81.33</v>
+      </c>
+      <c r="N14" s="6">
+        <v>58.09</v>
+      </c>
+      <c r="O14" s="11">
+        <v>67.77</v>
+      </c>
+      <c r="Q14" s="6">
+        <v>70.06</v>
+      </c>
+      <c r="R14" s="6">
+        <v>45.86</v>
+      </c>
+      <c r="S14" s="11">
+        <v>55.43</v>
+      </c>
+      <c r="U14" s="6">
+        <v>75.52</v>
+      </c>
+      <c r="V14" s="6">
+        <v>63.68</v>
+      </c>
+      <c r="W14" s="11">
+        <v>69.099999999999994</v>
+      </c>
+      <c r="Y14" s="6">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z14" s="6" t="e">
+        <v>78.267499999999998</v>
+      </c>
+      <c r="Z14" s="6">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA14" s="7" t="e">
+        <v>61.142499999999998</v>
+      </c>
+      <c r="AA14" s="7">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>68.397500000000008</v>
       </c>
     </row>
     <row r="15" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4244,6 +4340,13 @@
     <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="Y2:AA2"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="M2:O2"/>
+    <mergeCell ref="U2:W2"/>
     <mergeCell ref="AF17:AK17"/>
     <mergeCell ref="AM17:AR17"/>
     <mergeCell ref="I1:K1"/>
@@ -4251,13 +4354,6 @@
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="Y1:AA1"/>
     <mergeCell ref="M1:O1"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="Y2:AA2"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="M2:O2"/>
-    <mergeCell ref="U2:W2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/UniteD-SRL - run span.xlsx
+++ b/results/UniteD-SRL - run span.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\vito\SRL\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5C701CD-63B3-490A-82B0-72128B197DB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CF77777-063C-4E3F-89B5-331F3DB58F25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-75" yWindow="10440" windowWidth="38580" windowHeight="10545" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7785" yWindow="4845" windowWidth="20460" windowHeight="15045" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dependency-based" sheetId="1" r:id="rId1"/>
@@ -1465,21 +1465,53 @@
       <c r="G15" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="K15" s="11"/>
-      <c r="O15" s="11"/>
-      <c r="S15" s="11"/>
-      <c r="W15" s="11"/>
-      <c r="Y15" s="6" t="e">
+      <c r="I15" s="6">
+        <v>86.66</v>
+      </c>
+      <c r="J15" s="6">
+        <v>77.48</v>
+      </c>
+      <c r="K15" s="11">
+        <v>81.81</v>
+      </c>
+      <c r="M15" s="6">
+        <v>83.26</v>
+      </c>
+      <c r="N15" s="6">
+        <v>59.72</v>
+      </c>
+      <c r="O15" s="11">
+        <v>69.56</v>
+      </c>
+      <c r="Q15" s="6">
+        <v>76.55</v>
+      </c>
+      <c r="R15" s="6">
+        <v>71.72</v>
+      </c>
+      <c r="S15" s="11">
+        <v>74.06</v>
+      </c>
+      <c r="U15" s="6">
+        <v>75.239999999999995</v>
+      </c>
+      <c r="V15" s="6">
+        <v>63.34</v>
+      </c>
+      <c r="W15" s="11">
+        <v>68.78</v>
+      </c>
+      <c r="Y15" s="6">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z15" s="6" t="e">
+        <v>80.427500000000009</v>
+      </c>
+      <c r="Z15" s="6">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA15" s="7" t="e">
+        <v>68.064999999999998</v>
+      </c>
+      <c r="AA15" s="7">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>73.552500000000009</v>
       </c>
     </row>
     <row r="16" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4340,6 +4372,13 @@
     <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="AF17:AK17"/>
+    <mergeCell ref="AM17:AR17"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="Q1:S1"/>
+    <mergeCell ref="U1:W1"/>
+    <mergeCell ref="Y1:AA1"/>
+    <mergeCell ref="M1:O1"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="Q2:S2"/>
@@ -4347,13 +4386,6 @@
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="U2:W2"/>
-    <mergeCell ref="AF17:AK17"/>
-    <mergeCell ref="AM17:AR17"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="Q1:S1"/>
-    <mergeCell ref="U1:W1"/>
-    <mergeCell ref="Y1:AA1"/>
-    <mergeCell ref="M1:O1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/UniteD-SRL - run span.xlsx
+++ b/results/UniteD-SRL - run span.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\vito\SRL\results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lorpa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CF77777-063C-4E3F-89B5-331F3DB58F25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5DB16A4-6E6D-4918-A9EB-4298707FBAF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7785" yWindow="4845" windowWidth="20460" windowHeight="15045" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dependency-based" sheetId="1" r:id="rId1"/>
@@ -18,17 +18,6 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="O3dul5VTG9qJH6bckBMXuISjKzusumlk/3Xuqo2jwCo="/>
     </ext>
@@ -114,23 +103,27 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -482,23 +475,23 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AR967"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.5703125" customWidth="1"/>
-    <col min="2" max="7" width="7.7109375" customWidth="1"/>
+    <col min="1" max="1" width="21.54296875" customWidth="1"/>
+    <col min="2" max="7" width="7.7265625" customWidth="1"/>
     <col min="8" max="8" width="5" customWidth="1"/>
-    <col min="9" max="11" width="6.42578125" customWidth="1"/>
-    <col min="12" max="12" width="3.85546875" customWidth="1"/>
-    <col min="13" max="15" width="6.42578125" customWidth="1"/>
-    <col min="16" max="16" width="3.85546875" customWidth="1"/>
-    <col min="17" max="19" width="6.42578125" customWidth="1"/>
-    <col min="20" max="20" width="3.85546875" customWidth="1"/>
-    <col min="21" max="23" width="6.42578125" customWidth="1"/>
-    <col min="24" max="24" width="3.85546875" customWidth="1"/>
-    <col min="25" max="44" width="6.42578125" customWidth="1"/>
+    <col min="9" max="11" width="6.453125" customWidth="1"/>
+    <col min="12" max="12" width="3.81640625" customWidth="1"/>
+    <col min="13" max="15" width="6.453125" customWidth="1"/>
+    <col min="16" max="16" width="3.81640625" customWidth="1"/>
+    <col min="17" max="19" width="6.453125" customWidth="1"/>
+    <col min="20" max="20" width="3.81640625" customWidth="1"/>
+    <col min="21" max="23" width="6.453125" customWidth="1"/>
+    <col min="24" max="24" width="3.81640625" customWidth="1"/>
+    <col min="25" max="44" width="6.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -551,7 +544,7 @@
       <c r="AQ1" s="2"/>
       <c r="AR1" s="2"/>
     </row>
-    <row r="2" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="18" t="s">
         <v>5</v>
       </c>
@@ -608,7 +601,7 @@
       <c r="AQ2" s="2"/>
       <c r="AR2" s="2"/>
     </row>
-    <row r="3" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="17"/>
       <c r="B3" s="3" t="s">
         <v>8</v>
@@ -693,7 +686,7 @@
       <c r="AQ3" s="2"/>
       <c r="AR3" s="2"/>
     </row>
-    <row r="4" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>17</v>
       </c>
@@ -759,7 +752,7 @@
       <c r="AQ4" s="6"/>
       <c r="AR4" s="6"/>
     </row>
-    <row r="5" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
       <c r="B5" s="15" t="b">
         <v>0</v>
@@ -823,7 +816,7 @@
       <c r="AQ5" s="6"/>
       <c r="AR5" s="6"/>
     </row>
-    <row r="6" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="B6" s="15" t="b">
         <v>1</v>
@@ -844,30 +837,54 @@
         <v>0</v>
       </c>
       <c r="H6" s="1"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="7"/>
+      <c r="I6" s="6">
+        <v>86.38</v>
+      </c>
+      <c r="J6" s="6">
+        <v>77.430000000000007</v>
+      </c>
+      <c r="K6" s="7">
+        <v>81.66</v>
+      </c>
       <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="7"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="6"/>
-      <c r="S6" s="7"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="7"/>
-      <c r="Y6" s="6" t="e">
+      <c r="M6" s="6">
+        <v>83.18</v>
+      </c>
+      <c r="N6" s="6">
+        <v>60.95</v>
+      </c>
+      <c r="O6" s="7">
+        <v>70.349999999999994</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>66.2</v>
+      </c>
+      <c r="R6" s="6">
+        <v>52.29</v>
+      </c>
+      <c r="S6" s="7">
+        <v>58.43</v>
+      </c>
+      <c r="U6" s="6">
+        <v>62.45</v>
+      </c>
+      <c r="V6" s="6">
+        <v>29.23</v>
+      </c>
+      <c r="W6" s="7">
+        <v>39.82</v>
+      </c>
+      <c r="Y6" s="6">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z6" s="6" t="e">
+        <v>74.552499999999995</v>
+      </c>
+      <c r="Z6" s="6">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA6" s="7" t="e">
+        <v>54.974999999999994</v>
+      </c>
+      <c r="AA6" s="7">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>62.564999999999998</v>
       </c>
       <c r="AB6" s="6"/>
       <c r="AC6" s="6"/>
@@ -887,7 +904,7 @@
       <c r="AQ6" s="6"/>
       <c r="AR6" s="6"/>
     </row>
-    <row r="7" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
       <c r="B7" s="15" t="b">
         <v>1</v>
@@ -908,30 +925,54 @@
         <v>0</v>
       </c>
       <c r="H7" s="1"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="7"/>
+      <c r="I7" s="6">
+        <v>81.47</v>
+      </c>
+      <c r="J7" s="6">
+        <v>66.98</v>
+      </c>
+      <c r="K7" s="7">
+        <v>73.52</v>
+      </c>
       <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
-      <c r="O7" s="7"/>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="6"/>
-      <c r="S7" s="7"/>
-      <c r="U7" s="6"/>
-      <c r="V7" s="6"/>
-      <c r="W7" s="7"/>
-      <c r="Y7" s="6" t="e">
+      <c r="M7" s="6">
+        <v>78</v>
+      </c>
+      <c r="N7" s="6">
+        <v>50.34</v>
+      </c>
+      <c r="O7" s="7">
+        <v>61.19</v>
+      </c>
+      <c r="Q7" s="6">
+        <v>75.5</v>
+      </c>
+      <c r="R7" s="6">
+        <v>63.66</v>
+      </c>
+      <c r="S7" s="7">
+        <v>69.08</v>
+      </c>
+      <c r="U7" s="6">
+        <v>64.91</v>
+      </c>
+      <c r="V7" s="6">
+        <v>27.42</v>
+      </c>
+      <c r="W7" s="7">
+        <v>38.549999999999997</v>
+      </c>
+      <c r="Y7" s="6">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z7" s="6" t="e">
+        <v>74.97</v>
+      </c>
+      <c r="Z7" s="6">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA7" s="7" t="e">
+        <v>52.100000000000009</v>
+      </c>
+      <c r="AA7" s="7">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>60.584999999999994</v>
       </c>
       <c r="AB7" s="6"/>
       <c r="AC7" s="6"/>
@@ -951,7 +992,7 @@
       <c r="AQ7" s="6"/>
       <c r="AR7" s="6"/>
     </row>
-    <row r="8" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
       <c r="B8" s="15" t="b">
         <v>1</v>
@@ -972,30 +1013,54 @@
         <v>1</v>
       </c>
       <c r="H8" s="1"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="7"/>
+      <c r="I8" s="6">
+        <v>76.5</v>
+      </c>
+      <c r="J8" s="6">
+        <v>60.89</v>
+      </c>
+      <c r="K8" s="7">
+        <v>67.81</v>
+      </c>
       <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
-      <c r="O8" s="7"/>
-      <c r="Q8" s="6"/>
-      <c r="R8" s="6"/>
-      <c r="S8" s="7"/>
-      <c r="U8" s="6"/>
-      <c r="V8" s="6"/>
-      <c r="W8" s="7"/>
-      <c r="Y8" s="6" t="e">
+      <c r="M8" s="6">
+        <v>81.84</v>
+      </c>
+      <c r="N8" s="6">
+        <v>52.42</v>
+      </c>
+      <c r="O8" s="7">
+        <v>63.9</v>
+      </c>
+      <c r="Q8" s="6">
+        <v>68.92</v>
+      </c>
+      <c r="R8" s="6">
+        <v>42.92</v>
+      </c>
+      <c r="S8" s="7">
+        <v>52.9</v>
+      </c>
+      <c r="U8" s="6">
+        <v>74.680000000000007</v>
+      </c>
+      <c r="V8" s="6">
+        <v>62.44</v>
+      </c>
+      <c r="W8" s="7">
+        <v>68.02</v>
+      </c>
+      <c r="Y8" s="6">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z8" s="6" t="e">
+        <v>75.484999999999999</v>
+      </c>
+      <c r="Z8" s="6">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA8" s="7" t="e">
+        <v>54.667500000000004</v>
+      </c>
+      <c r="AA8" s="7">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>63.157499999999999</v>
       </c>
       <c r="AB8" s="6"/>
       <c r="AC8" s="6"/>
@@ -1015,7 +1080,7 @@
       <c r="AQ8" s="6"/>
       <c r="AR8" s="6"/>
     </row>
-    <row r="9" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="B9" s="15" t="b">
         <v>1</v>
@@ -1036,30 +1101,54 @@
         <v>1</v>
       </c>
       <c r="H9" s="1"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="7"/>
+      <c r="I9" s="6">
+        <v>86.89</v>
+      </c>
+      <c r="J9" s="6">
+        <v>76.94</v>
+      </c>
+      <c r="K9" s="7">
+        <v>81.61</v>
+      </c>
       <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="7"/>
-      <c r="Q9" s="6"/>
-      <c r="R9" s="6"/>
-      <c r="S9" s="7"/>
-      <c r="U9" s="6"/>
-      <c r="V9" s="6"/>
-      <c r="W9" s="7"/>
-      <c r="Y9" s="6" t="e">
+      <c r="M9" s="6">
+        <v>82.7</v>
+      </c>
+      <c r="N9" s="6">
+        <v>60</v>
+      </c>
+      <c r="O9" s="7">
+        <v>69.55</v>
+      </c>
+      <c r="Q9" s="6">
+        <v>77.72</v>
+      </c>
+      <c r="R9" s="6">
+        <v>71.209999999999994</v>
+      </c>
+      <c r="S9" s="7">
+        <v>74.319999999999993</v>
+      </c>
+      <c r="U9" s="6">
+        <v>74.58</v>
+      </c>
+      <c r="V9" s="6">
+        <v>62.57</v>
+      </c>
+      <c r="W9" s="7">
+        <v>68.05</v>
+      </c>
+      <c r="Y9" s="6">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z9" s="6" t="e">
+        <v>80.472499999999997</v>
+      </c>
+      <c r="Z9" s="6">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA9" s="7" t="e">
+        <v>67.679999999999993</v>
+      </c>
+      <c r="AA9" s="7">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>73.382499999999993</v>
       </c>
       <c r="AB9" s="6"/>
       <c r="AC9" s="6"/>
@@ -1079,7 +1168,7 @@
       <c r="AQ9" s="6"/>
       <c r="AR9" s="6"/>
     </row>
-    <row r="10" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
         <v>18</v>
       </c>
@@ -1169,7 +1258,7 @@
       <c r="AQ10" s="6"/>
       <c r="AR10" s="6"/>
     </row>
-    <row r="11" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10"/>
       <c r="B11" s="15" t="b">
         <v>0</v>
@@ -1238,7 +1327,7 @@
         <v>33.892499999999998</v>
       </c>
     </row>
-    <row r="12" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10"/>
       <c r="B12" s="15" t="b">
         <v>1</v>
@@ -1307,7 +1396,7 @@
         <v>61.75</v>
       </c>
     </row>
-    <row r="13" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="10"/>
       <c r="B13" s="15" t="b">
         <v>1</v>
@@ -1376,7 +1465,7 @@
         <v>64.864999999999995</v>
       </c>
     </row>
-    <row r="14" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10"/>
       <c r="B14" s="15" t="b">
         <v>1</v>
@@ -1445,7 +1534,7 @@
         <v>68.397500000000008</v>
       </c>
     </row>
-    <row r="15" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="10"/>
       <c r="B15" s="15" t="b">
         <v>1</v>
@@ -1514,7 +1603,7 @@
         <v>73.552500000000009</v>
       </c>
     </row>
-    <row r="16" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -1553,7 +1642,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="17" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="13"/>
       <c r="B17" s="15" t="b">
         <v>0</v>
@@ -1620,956 +1709,956 @@
       <c r="AQ17" s="17"/>
       <c r="AR17" s="17"/>
     </row>
-    <row r="18" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="19" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="20" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="21" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="18" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="14">
     <mergeCell ref="AM17:AR17"/>
@@ -2597,23 +2686,23 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AR974"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.5703125" customWidth="1"/>
-    <col min="2" max="7" width="6.42578125" customWidth="1"/>
+    <col min="1" max="1" width="21.54296875" customWidth="1"/>
+    <col min="2" max="7" width="6.453125" customWidth="1"/>
     <col min="8" max="8" width="5" customWidth="1"/>
-    <col min="9" max="11" width="6.42578125" customWidth="1"/>
-    <col min="12" max="12" width="3.85546875" customWidth="1"/>
-    <col min="13" max="15" width="6.42578125" customWidth="1"/>
-    <col min="16" max="16" width="3.85546875" customWidth="1"/>
-    <col min="17" max="19" width="6.42578125" customWidth="1"/>
-    <col min="20" max="20" width="3.85546875" customWidth="1"/>
-    <col min="21" max="23" width="6.42578125" customWidth="1"/>
-    <col min="24" max="24" width="3.85546875" customWidth="1"/>
-    <col min="25" max="44" width="6.42578125" customWidth="1"/>
+    <col min="9" max="11" width="6.453125" customWidth="1"/>
+    <col min="12" max="12" width="3.81640625" customWidth="1"/>
+    <col min="13" max="15" width="6.453125" customWidth="1"/>
+    <col min="16" max="16" width="3.81640625" customWidth="1"/>
+    <col min="17" max="19" width="6.453125" customWidth="1"/>
+    <col min="20" max="20" width="3.81640625" customWidth="1"/>
+    <col min="21" max="23" width="6.453125" customWidth="1"/>
+    <col min="24" max="24" width="3.81640625" customWidth="1"/>
+    <col min="25" max="44" width="6.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2666,7 +2755,7 @@
       <c r="AQ1" s="2"/>
       <c r="AR1" s="2"/>
     </row>
-    <row r="2" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="18" t="s">
         <v>5</v>
       </c>
@@ -2723,7 +2812,7 @@
       <c r="AQ2" s="2"/>
       <c r="AR2" s="2"/>
     </row>
-    <row r="3" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="17"/>
       <c r="B3" s="3" t="s">
         <v>8</v>
@@ -2808,7 +2897,7 @@
       <c r="AQ3" s="2"/>
       <c r="AR3" s="2"/>
     </row>
-    <row r="4" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>17</v>
       </c>
@@ -2865,7 +2954,7 @@
       <c r="AQ4" s="6"/>
       <c r="AR4" s="6"/>
     </row>
-    <row r="5" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
       <c r="B5" s="1" t="b">
         <v>0</v>
@@ -2920,7 +3009,7 @@
       <c r="AQ5" s="6"/>
       <c r="AR5" s="6"/>
     </row>
-    <row r="6" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="B6" s="1" t="b">
         <v>1</v>
@@ -2975,7 +3064,7 @@
       <c r="AQ6" s="6"/>
       <c r="AR6" s="6"/>
     </row>
-    <row r="7" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
       <c r="B7" s="1" t="b">
         <v>1</v>
@@ -3030,7 +3119,7 @@
       <c r="AQ7" s="6"/>
       <c r="AR7" s="6"/>
     </row>
-    <row r="8" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
       <c r="B8" s="1" t="b">
         <v>1</v>
@@ -3085,7 +3174,7 @@
       <c r="AQ8" s="6"/>
       <c r="AR8" s="6"/>
     </row>
-    <row r="9" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="B9" s="1" t="b">
         <v>1</v>
@@ -3140,7 +3229,7 @@
       <c r="AQ9" s="6"/>
       <c r="AR9" s="6"/>
     </row>
-    <row r="10" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
         <v>18</v>
       </c>
@@ -3197,7 +3286,7 @@
       <c r="AQ10" s="6"/>
       <c r="AR10" s="6"/>
     </row>
-    <row r="11" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10"/>
       <c r="B11" s="1" t="b">
         <v>0</v>
@@ -3223,7 +3312,7 @@
       <c r="W11" s="11"/>
       <c r="AA11" s="11"/>
     </row>
-    <row r="12" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10"/>
       <c r="B12" s="1" t="b">
         <v>1</v>
@@ -3249,7 +3338,7 @@
       <c r="W12" s="11"/>
       <c r="AA12" s="11"/>
     </row>
-    <row r="13" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="10"/>
       <c r="B13" s="1" t="b">
         <v>1</v>
@@ -3275,7 +3364,7 @@
       <c r="W13" s="11"/>
       <c r="AA13" s="11"/>
     </row>
-    <row r="14" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10"/>
       <c r="B14" s="1" t="b">
         <v>1</v>
@@ -3301,7 +3390,7 @@
       <c r="W14" s="11"/>
       <c r="AA14" s="11"/>
     </row>
-    <row r="15" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="10"/>
       <c r="B15" s="1" t="b">
         <v>1</v>
@@ -3327,7 +3416,7 @@
       <c r="W15" s="11"/>
       <c r="AA15" s="11"/>
     </row>
-    <row r="16" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -3355,7 +3444,7 @@
       <c r="W16" s="11"/>
       <c r="AA16" s="11"/>
     </row>
-    <row r="17" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="13"/>
       <c r="B17" s="1" t="b">
         <v>0</v>
@@ -3413,963 +3502,963 @@
       <c r="AQ17" s="17"/>
       <c r="AR17" s="17"/>
     </row>
-    <row r="18" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="19" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="20" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="21" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="18" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="14">
     <mergeCell ref="AF17:AK17"/>

--- a/results/UniteD-SRL - run span.xlsx
+++ b/results/UniteD-SRL - run span.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lorpa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5DB16A4-6E6D-4918-A9EB-4298707FBAF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{877721C0-D82D-4926-83E9-AA1F1CD42559}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -709,30 +709,54 @@
         <v>0</v>
       </c>
       <c r="H4" s="1"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="7"/>
+      <c r="I4" s="6">
+        <v>1.68</v>
+      </c>
+      <c r="J4" s="6">
+        <v>22.05</v>
+      </c>
+      <c r="K4" s="7">
+        <v>0</v>
+      </c>
       <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="7"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
-      <c r="S4" s="7"/>
-      <c r="U4" s="6"/>
-      <c r="V4" s="6"/>
-      <c r="W4" s="7"/>
-      <c r="Y4" s="6" t="e">
+      <c r="M4" s="6">
+        <v>2.38</v>
+      </c>
+      <c r="N4" s="6">
+        <v>25.17</v>
+      </c>
+      <c r="O4" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="6">
+        <v>6.68</v>
+      </c>
+      <c r="R4" s="6">
+        <v>42.32</v>
+      </c>
+      <c r="S4" s="7">
+        <v>0</v>
+      </c>
+      <c r="U4" s="6">
+        <v>8.1199999999999992</v>
+      </c>
+      <c r="V4" s="6">
+        <v>45.74</v>
+      </c>
+      <c r="W4" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="6">
         <f t="shared" ref="Y4:Y9" si="0">AVERAGE(I4,M4,Q4,U4)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z4" s="6" t="e">
+        <v>4.7149999999999999</v>
+      </c>
+      <c r="Z4" s="6">
         <f t="shared" ref="Z4:Z9" si="1">AVERAGE(J4,N4,R4,V4)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA4" s="7" t="e">
+        <v>33.82</v>
+      </c>
+      <c r="AA4" s="7">
         <f t="shared" ref="AA4:AA9" si="2">AVERAGE(K4,O4,S4,W4)</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="AB4" s="6"/>
       <c r="AC4" s="6"/>
@@ -773,30 +797,54 @@
         <v>0</v>
       </c>
       <c r="H5" s="1"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="7"/>
+      <c r="I5" s="6">
+        <v>1.38</v>
+      </c>
+      <c r="J5" s="6">
+        <v>15.05</v>
+      </c>
+      <c r="K5" s="7">
+        <v>0</v>
+      </c>
       <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="7"/>
-      <c r="Q5" s="6"/>
-      <c r="R5" s="6"/>
-      <c r="S5" s="7"/>
-      <c r="U5" s="6"/>
-      <c r="V5" s="6"/>
-      <c r="W5" s="7"/>
-      <c r="Y5" s="6" t="e">
+      <c r="M5" s="6">
+        <v>1.78</v>
+      </c>
+      <c r="N5" s="6">
+        <v>14.94</v>
+      </c>
+      <c r="O5" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="6">
+        <v>1.06</v>
+      </c>
+      <c r="R5" s="6">
+        <v>14.78</v>
+      </c>
+      <c r="S5" s="7">
+        <v>0</v>
+      </c>
+      <c r="U5" s="6">
+        <v>0.89</v>
+      </c>
+      <c r="V5" s="6">
+        <v>14.73</v>
+      </c>
+      <c r="W5" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="6">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z5" s="6" t="e">
+        <v>1.2775000000000001</v>
+      </c>
+      <c r="Z5" s="6">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA5" s="7" t="e">
+        <v>14.875</v>
+      </c>
+      <c r="AA5" s="7">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="AB5" s="6"/>
       <c r="AC5" s="6"/>
@@ -4461,6 +4509,13 @@
     <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="Y2:AA2"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="M2:O2"/>
+    <mergeCell ref="U2:W2"/>
     <mergeCell ref="AF17:AK17"/>
     <mergeCell ref="AM17:AR17"/>
     <mergeCell ref="I1:K1"/>
@@ -4468,13 +4523,6 @@
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="Y1:AA1"/>
     <mergeCell ref="M1:O1"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="Y2:AA2"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="M2:O2"/>
-    <mergeCell ref="U2:W2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/UniteD-SRL - run span.xlsx
+++ b/results/UniteD-SRL - run span.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lorpa\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lorpa\Documents\Università\Magistrale\Anno2\TESI\project\SRL\SRL\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{877721C0-D82D-4926-83E9-AA1F1CD42559}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D717C43D-C8C1-4378-99EC-2C6BBA294CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -710,53 +710,53 @@
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="6">
-        <v>1.68</v>
+        <v>61.11</v>
       </c>
       <c r="J4" s="6">
-        <v>22.05</v>
+        <v>12.9</v>
       </c>
       <c r="K4" s="7">
-        <v>0</v>
+        <v>21.3</v>
       </c>
       <c r="L4" s="6"/>
       <c r="M4" s="6">
-        <v>2.38</v>
+        <v>37.08</v>
       </c>
       <c r="N4" s="6">
-        <v>25.17</v>
+        <v>0.25</v>
       </c>
       <c r="O4" s="7">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q4" s="6">
-        <v>6.68</v>
+        <v>50.39</v>
       </c>
       <c r="R4" s="6">
-        <v>42.32</v>
+        <v>5.4</v>
       </c>
       <c r="S4" s="7">
-        <v>0</v>
+        <v>9.7899999999999991</v>
       </c>
       <c r="U4" s="6">
-        <v>8.1199999999999992</v>
+        <v>56.5</v>
       </c>
       <c r="V4" s="6">
-        <v>45.74</v>
+        <v>3.97</v>
       </c>
       <c r="W4" s="7">
-        <v>0</v>
+        <v>7.42</v>
       </c>
       <c r="Y4" s="6">
         <f t="shared" ref="Y4:Y9" si="0">AVERAGE(I4,M4,Q4,U4)</f>
-        <v>4.7149999999999999</v>
+        <v>51.269999999999996</v>
       </c>
       <c r="Z4" s="6">
         <f t="shared" ref="Z4:Z9" si="1">AVERAGE(J4,N4,R4,V4)</f>
-        <v>33.82</v>
+        <v>5.63</v>
       </c>
       <c r="AA4" s="7">
         <f t="shared" ref="AA4:AA9" si="2">AVERAGE(K4,O4,S4,W4)</f>
-        <v>0</v>
+        <v>9.7524999999999995</v>
       </c>
       <c r="AB4" s="6"/>
       <c r="AC4" s="6"/>
@@ -798,53 +798,53 @@
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="6">
-        <v>1.38</v>
+        <v>33.21</v>
       </c>
       <c r="J5" s="6">
-        <v>15.05</v>
+        <v>1.7</v>
       </c>
       <c r="K5" s="7">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="L5" s="6"/>
       <c r="M5" s="6">
-        <v>1.78</v>
+        <v>51.65</v>
       </c>
       <c r="N5" s="6">
-        <v>14.94</v>
+        <v>8.9499999999999993</v>
       </c>
       <c r="O5" s="7">
-        <v>0</v>
+        <v>15.26</v>
       </c>
       <c r="Q5" s="6">
-        <v>1.06</v>
+        <v>28.21</v>
       </c>
       <c r="R5" s="6">
-        <v>14.78</v>
+        <v>0.64</v>
       </c>
       <c r="S5" s="7">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="U5" s="6">
-        <v>0.89</v>
+        <v>33.76</v>
       </c>
       <c r="V5" s="6">
-        <v>14.73</v>
+        <v>0.74</v>
       </c>
       <c r="W5" s="7">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Y5" s="6">
         <f t="shared" si="0"/>
-        <v>1.2775000000000001</v>
+        <v>36.707499999999996</v>
       </c>
       <c r="Z5" s="6">
         <f t="shared" si="1"/>
-        <v>14.875</v>
+        <v>3.0074999999999998</v>
       </c>
       <c r="AA5" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5.3025000000000002</v>
       </c>
       <c r="AB5" s="6"/>
       <c r="AC5" s="6"/>
@@ -4509,6 +4509,13 @@
     <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="AF17:AK17"/>
+    <mergeCell ref="AM17:AR17"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="Q1:S1"/>
+    <mergeCell ref="U1:W1"/>
+    <mergeCell ref="Y1:AA1"/>
+    <mergeCell ref="M1:O1"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="Q2:S2"/>
@@ -4516,13 +4523,6 @@
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="U2:W2"/>
-    <mergeCell ref="AF17:AK17"/>
-    <mergeCell ref="AM17:AR17"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="Q1:S1"/>
-    <mergeCell ref="U1:W1"/>
-    <mergeCell ref="Y1:AA1"/>
-    <mergeCell ref="M1:O1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
